--- a/Test/Resource/TestData_File_5_part1.xlsx
+++ b/Test/Resource/TestData_File_5_part1.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Simran</t>
+          <t>Raj</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -466,7 +466,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Development</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Raj</t>
+          <t>Riya</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Raj</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amol</t>
+          <t>Rohan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Support</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vikas</t>
+          <t>Raj</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Riya</t>
+          <t>Rohan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>QA</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amit</t>
+          <t>Amol</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Development</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Amol</t>
+          <t>Rohan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Neha</t>
+          <t>Amit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rohan</t>
+          <t>Priya</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Support</t>
         </is>
       </c>
     </row>
